--- a/SLR/Full-Paper-Read/Paper-Review/PS11.xlsx
+++ b/SLR/Full-Paper-Read/Paper-Review/PS11.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="60">
   <si>
     <t>ID</t>
   </si>
@@ -26,8 +26,7 @@
     <t>The paper proposes the following contributions:</t>
   </si>
   <si>
-    <t>Motivation: This paper aims at describing how the design and implementation of a multi-sided platform (MSP) for CPS deployment within the automation sector can provide the technological background to incentivize their adoption. Developing an infrastructure on the top of which the CPS value chain can be instantiated and orchestrated, the authors provide the technical means to incentivize the creation of an ecosystem able to support SMEs in their transition towards Industry 4.0.
-Contribution: Digital marketplace developed for the DAEDALUS (Distributed control and simulAtion platform to support an Ecosystem of DigitAL aUtomation developerS) H2020 project.</t>
+    <t xml:space="preserve">The paper introduces a Real-time Linked Dataspace (RLD) as an enabling platform for data management within smart environments. This paper identifies common data management requirements for smart energy and water environments, details the RLD architecture and the key support services and their tiered support levels, and a principled approach to ‘‘Pay-As-You-Go’’ data management. The paper presents a dataspace query service for real-time data streams and entities to enable unified entity-centric queries across live and historical stream data. </t>
   </si>
   <si>
     <t>&lt;add your comment here if any&gt;</t>
@@ -36,7 +35,7 @@
     <t>CPS Case Study / Example availability</t>
   </si>
   <si>
-    <t>Digital marketplace: certification process</t>
+    <t>Five pilots for smart energy and water management systems in smart buildings: Smart Airport, Smart Office, Smart Homes, Mixed Use, Smart School</t>
   </si>
   <si>
     <t>SECO Tools Availability (add repository or website in the comment)</t>
@@ -45,45 +44,46 @@
     <t>N</t>
   </si>
   <si>
-    <t>Architecture presented, no external source</t>
-  </si>
-  <si>
     <t>Related Challenge - See SPE paper (Write Others in comment cell)</t>
   </si>
   <si>
     <t>Data</t>
   </si>
   <si>
+    <t>Requirements engineering</t>
+  </si>
+  <si>
     <t>Intelligence and automation</t>
   </si>
   <si>
+    <t>n.a.</t>
+  </si>
+  <si>
+    <t>Does it contribute to answer RQ1?</t>
+  </si>
+  <si>
+    <t>Not during the CPS development, but challenges in data management in smart environments</t>
+  </si>
+  <si>
+    <t>Does the paper present methods, tools, and benefits in terms of industry/academia collaboration? If so, write what methods, tools, and benefits in the comment column</t>
+  </si>
+  <si>
+    <t>No mention of industry-academia collaboration.</t>
+  </si>
+  <si>
+    <t>Does it contribute to answer RQ2?</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Application Domain(s) (at least one or domain independent)</t>
+  </si>
+  <si>
     <t>Others</t>
   </si>
   <si>
-    <t>n.a.</t>
-  </si>
-  <si>
-    <t>The fundamental layer, on which the rest of the architecture is based on, is the Persistency Layer which is composed by the repositories and the Persistency Manager. The Repository represents the knowledge base of the Marketplace and it’s composed by the hosted CPS(s), the Economic Data Model, meant to describe all economic aspects of the products (pricing strategies, fees, etc.) and the Semantic Data Model meant to characterize the submitted product in order to be accurately searched and identified. The Semantic Data Model is managed by the Product Manager component which is also in charge to provide discovery functionalities of the hosted products.
-Digital Automation
-Market uptake</t>
-  </si>
-  <si>
-    <t>Does it contribute to answer RQ1?</t>
-  </si>
-  <si>
-    <t>Y</t>
-  </si>
-  <si>
-    <t>Does the paper present methods, tools, and benefits in terms of industry/academia collaboration? If so, write what methods, tools, and benefits in the comment column</t>
-  </si>
-  <si>
-    <t>Does it contribute to answer RQ2?</t>
-  </si>
-  <si>
-    <t>Application Domain(s) (at least one or domain independent)</t>
-  </si>
-  <si>
-    <t>Manufacturing</t>
+    <t>Smart energy and water management systems</t>
   </si>
   <si>
     <t>Quality Evaluation (From 1 to 10) - From "Quality" Tab</t>
@@ -174,9 +174,6 @@
   </si>
   <si>
     <t>Is the study replicable?</t>
-  </si>
-  <si>
-    <t>0,5</t>
   </si>
   <si>
     <t>Has sufficient data been presented to support the findings?</t>
@@ -565,7 +562,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="60">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -604,20 +601,20 @@
       <alignment horizontal="right"/>
     </xf>
     <xf borderId="18" fillId="5" fontId="3" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
+      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="16" fillId="3" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right"/>
     </xf>
     <xf borderId="18" fillId="3" fontId="3" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
+      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="19" fillId="3" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" readingOrder="0"/>
     </xf>
     <xf borderId="20" fillId="4" fontId="1" numFmtId="1" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="18" fillId="3" fontId="3" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
+      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="16" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
@@ -629,7 +626,7 @@
       <alignment horizontal="right"/>
     </xf>
     <xf borderId="18" fillId="5" fontId="3" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
+      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="21" fillId="3" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" readingOrder="0"/>
@@ -665,7 +662,7 @@
       <alignment vertical="bottom"/>
     </xf>
     <xf borderId="25" fillId="7" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
+      <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right" vertical="bottom"/>
@@ -681,12 +678,24 @@
     <xf borderId="25" fillId="8" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
+    <xf borderId="25" fillId="8" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" vertical="bottom"/>
+    </xf>
+    <xf borderId="25" fillId="8" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
+    </xf>
     <xf borderId="24" fillId="9" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" textRotation="90"/>
     </xf>
     <xf borderId="25" fillId="9" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
+    <xf borderId="25" fillId="9" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" vertical="bottom"/>
+    </xf>
+    <xf borderId="25" fillId="9" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
@@ -695,6 +704,9 @@
     </xf>
     <xf borderId="25" fillId="10" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="25" fillId="10" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyFont="1"/>
   </cellXfs>
@@ -994,7 +1006,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" ht="154.5" customHeight="1">
+    <row r="3" ht="82.5" customHeight="1">
       <c r="A3" s="10"/>
       <c r="B3" s="11"/>
       <c r="C3" s="12"/>
@@ -1040,36 +1052,36 @@
       <c r="G5" s="18"/>
       <c r="H5" s="18"/>
       <c r="I5" s="21" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" ht="15.75" customHeight="1">
       <c r="A6" s="16">
         <v>4.0</v>
       </c>
       <c r="B6" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="17" t="s">
+      <c r="D6" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="17" t="s">
+      <c r="E6" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="E6" s="17" t="s">
+      <c r="F6" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="F6" s="22" t="s">
-        <v>15</v>
-      </c>
       <c r="G6" s="22" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H6" s="22" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I6" s="23" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1">
@@ -1077,10 +1089,10 @@
         <v>5.0</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C7" s="24" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="D7" s="25"/>
       <c r="E7" s="25"/>
@@ -1088,7 +1100,7 @@
       <c r="G7" s="25"/>
       <c r="H7" s="18"/>
       <c r="I7" s="26" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8">
@@ -1096,7 +1108,7 @@
         <v>6.0</v>
       </c>
       <c r="B8" s="27" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C8" s="28" t="s">
         <v>9</v>
@@ -1107,7 +1119,7 @@
       <c r="G8" s="25"/>
       <c r="H8" s="18"/>
       <c r="I8" s="26" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9" ht="15.75" customHeight="1">
@@ -1115,7 +1127,7 @@
         <v>7.0</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C9" s="29" t="s">
         <v>9</v>
@@ -1126,7 +1138,7 @@
       <c r="G9" s="25"/>
       <c r="H9" s="18"/>
       <c r="I9" s="30" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10" ht="15.75" customHeight="1">
@@ -1140,22 +1152,22 @@
         <v>22</v>
       </c>
       <c r="D10" s="32" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E10" s="32" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F10" s="32" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G10" s="32" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H10" s="32" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I10" s="26" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="11" ht="15.75" customHeight="1">
@@ -1163,30 +1175,30 @@
         <v>9.0</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C11" s="33">
         <f>Quality!C29</f>
-        <v>6.296296296</v>
+        <v>8.703703704</v>
       </c>
       <c r="D11" s="25"/>
       <c r="E11" s="25"/>
       <c r="F11" s="25"/>
       <c r="G11" s="25"/>
       <c r="H11" s="25"/>
-      <c r="I11" s="30" t="s">
+      <c r="I11" s="21" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="12" ht="15.75" customHeight="1"/>
     <row r="14" ht="15.75" customHeight="1">
       <c r="B14" s="34" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1">
       <c r="B15" s="34" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="16" ht="15.75" customHeight="1"/>
@@ -2247,10 +2259,10 @@
     <row r="1">
       <c r="A1" s="35"/>
       <c r="B1" s="36" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C1" s="36" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D1" s="37"/>
       <c r="E1" s="38"/>
@@ -2258,10 +2270,10 @@
     </row>
     <row r="2">
       <c r="A2" s="40" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B2" s="41" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C2" s="42">
         <v>1.0</v>
@@ -2273,7 +2285,7 @@
     <row r="3">
       <c r="A3" s="44"/>
       <c r="B3" s="41" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C3" s="42">
         <v>1.0</v>
@@ -2285,7 +2297,7 @@
     <row r="4">
       <c r="A4" s="44"/>
       <c r="B4" s="41" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C4" s="42">
         <v>1.0</v>
@@ -2296,7 +2308,7 @@
     <row r="5">
       <c r="A5" s="44"/>
       <c r="B5" s="41" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C5" s="42">
         <v>1.0</v>
@@ -2307,10 +2319,10 @@
     <row r="6">
       <c r="A6" s="44"/>
       <c r="B6" s="41" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C6" s="42">
-        <v>0.5</v>
+        <v>1.0</v>
       </c>
       <c r="D6" s="37"/>
       <c r="E6" s="37"/>
@@ -2318,10 +2330,10 @@
     <row r="7">
       <c r="A7" s="45"/>
       <c r="B7" s="41" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C7" s="42">
-        <v>0.5</v>
+        <v>1.0</v>
       </c>
       <c r="D7" s="46">
         <f>COUNTIF(B2:B7,"&lt;&gt;text")</f>
@@ -2329,18 +2341,18 @@
       </c>
       <c r="E7" s="46">
         <f>(SUM(C2:C7)/D7)*10</f>
-        <v>8.333333333</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="47" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B8" s="48" t="s">
-        <v>36</v>
-      </c>
-      <c r="C8" s="42">
-        <v>0.5</v>
+        <v>37</v>
+      </c>
+      <c r="C8" s="49">
+        <v>1.0</v>
       </c>
       <c r="D8" s="37"/>
       <c r="E8" s="37"/>
@@ -2348,10 +2360,10 @@
     <row r="9">
       <c r="A9" s="44"/>
       <c r="B9" s="48" t="s">
-        <v>37</v>
-      </c>
-      <c r="C9" s="42">
-        <v>0.5</v>
+        <v>38</v>
+      </c>
+      <c r="C9" s="49">
+        <v>1.0</v>
       </c>
       <c r="D9" s="37"/>
       <c r="E9" s="37"/>
@@ -2359,10 +2371,10 @@
     <row r="10">
       <c r="A10" s="44"/>
       <c r="B10" s="48" t="s">
-        <v>38</v>
-      </c>
-      <c r="C10" s="42">
-        <v>0.5</v>
+        <v>39</v>
+      </c>
+      <c r="C10" s="49">
+        <v>1.0</v>
       </c>
       <c r="D10" s="37"/>
       <c r="E10" s="37"/>
@@ -2370,9 +2382,9 @@
     <row r="11">
       <c r="A11" s="44"/>
       <c r="B11" s="48" t="s">
-        <v>39</v>
-      </c>
-      <c r="C11" s="42">
+        <v>40</v>
+      </c>
+      <c r="C11" s="50">
         <v>0.5</v>
       </c>
       <c r="D11" s="37"/>
@@ -2381,10 +2393,10 @@
     <row r="12">
       <c r="A12" s="44"/>
       <c r="B12" s="48" t="s">
-        <v>40</v>
-      </c>
-      <c r="C12" s="42">
-        <v>0.5</v>
+        <v>41</v>
+      </c>
+      <c r="C12" s="49">
+        <v>1.0</v>
       </c>
       <c r="D12" s="37"/>
       <c r="E12" s="37"/>
@@ -2392,10 +2404,10 @@
     <row r="13">
       <c r="A13" s="44"/>
       <c r="B13" s="48" t="s">
-        <v>41</v>
-      </c>
-      <c r="C13" s="42">
-        <v>0.5</v>
+        <v>42</v>
+      </c>
+      <c r="C13" s="49">
+        <v>1.0</v>
       </c>
       <c r="D13" s="37"/>
       <c r="E13" s="37"/>
@@ -2403,10 +2415,10 @@
     <row r="14">
       <c r="A14" s="44"/>
       <c r="B14" s="48" t="s">
-        <v>42</v>
-      </c>
-      <c r="C14" s="42">
-        <v>0.5</v>
+        <v>43</v>
+      </c>
+      <c r="C14" s="49">
+        <v>1.0</v>
       </c>
       <c r="D14" s="37"/>
       <c r="E14" s="37"/>
@@ -2414,9 +2426,9 @@
     <row r="15">
       <c r="A15" s="44"/>
       <c r="B15" s="48" t="s">
-        <v>43</v>
-      </c>
-      <c r="C15" s="42">
+        <v>44</v>
+      </c>
+      <c r="C15" s="50">
         <v>0.5</v>
       </c>
       <c r="D15" s="37"/>
@@ -2425,9 +2437,9 @@
     <row r="16">
       <c r="A16" s="44"/>
       <c r="B16" s="48" t="s">
-        <v>44</v>
-      </c>
-      <c r="C16" s="42">
+        <v>45</v>
+      </c>
+      <c r="C16" s="50">
         <v>0.5</v>
       </c>
       <c r="D16" s="37"/>
@@ -2436,9 +2448,9 @@
     <row r="17">
       <c r="A17" s="44"/>
       <c r="B17" s="48" t="s">
-        <v>45</v>
-      </c>
-      <c r="C17" s="42">
+        <v>46</v>
+      </c>
+      <c r="C17" s="49">
         <v>1.0</v>
       </c>
       <c r="D17" s="37"/>
@@ -2447,10 +2459,10 @@
     <row r="18">
       <c r="A18" s="44"/>
       <c r="B18" s="48" t="s">
-        <v>46</v>
-      </c>
-      <c r="C18" s="42">
-        <v>0.5</v>
+        <v>47</v>
+      </c>
+      <c r="C18" s="49">
+        <v>1.0</v>
       </c>
       <c r="D18" s="37"/>
       <c r="E18" s="37"/>
@@ -2458,10 +2470,10 @@
     <row r="19">
       <c r="A19" s="45"/>
       <c r="B19" s="48" t="s">
-        <v>47</v>
-      </c>
-      <c r="C19" s="42">
-        <v>0.5</v>
+        <v>48</v>
+      </c>
+      <c r="C19" s="49">
+        <v>1.0</v>
       </c>
       <c r="D19" s="46">
         <f>COUNTIF(B8:B19,"&lt;&gt;text")</f>
@@ -2469,28 +2481,28 @@
       </c>
       <c r="E19" s="46">
         <f>(SUM(C8:C19)/D19)*10</f>
-        <v>5.416666667</v>
+        <v>8.75</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="49" t="s">
-        <v>48</v>
-      </c>
-      <c r="B20" s="50" t="s">
+      <c r="A20" s="51" t="s">
         <v>49</v>
       </c>
-      <c r="C20" s="42">
-        <v>0.5</v>
+      <c r="B20" s="52" t="s">
+        <v>50</v>
+      </c>
+      <c r="C20" s="53">
+        <v>1.0</v>
       </c>
       <c r="D20" s="37"/>
       <c r="E20" s="37"/>
     </row>
     <row r="21">
       <c r="A21" s="44"/>
-      <c r="B21" s="50" t="s">
-        <v>50</v>
-      </c>
-      <c r="C21" s="42">
+      <c r="B21" s="52" t="s">
+        <v>51</v>
+      </c>
+      <c r="C21" s="54">
         <v>0.5</v>
       </c>
       <c r="D21" s="37"/>
@@ -2498,22 +2510,22 @@
     </row>
     <row r="22">
       <c r="A22" s="44"/>
-      <c r="B22" s="50" t="s">
-        <v>51</v>
-      </c>
-      <c r="C22" s="42">
-        <v>0.5</v>
+      <c r="B22" s="52" t="s">
+        <v>52</v>
+      </c>
+      <c r="C22" s="54">
+        <v>0.0</v>
       </c>
       <c r="D22" s="37"/>
       <c r="E22" s="37"/>
     </row>
     <row r="23">
       <c r="A23" s="44"/>
-      <c r="B23" s="50" t="s">
-        <v>52</v>
-      </c>
-      <c r="C23" s="42" t="s">
+      <c r="B23" s="52" t="s">
         <v>53</v>
+      </c>
+      <c r="C23" s="54">
+        <v>0.5</v>
       </c>
       <c r="D23" s="38"/>
       <c r="E23" s="38"/>
@@ -2521,10 +2533,10 @@
     </row>
     <row r="24">
       <c r="A24" s="44"/>
-      <c r="B24" s="50" t="s">
+      <c r="B24" s="52" t="s">
         <v>54</v>
       </c>
-      <c r="C24" s="42">
+      <c r="C24" s="53">
         <v>1.0</v>
       </c>
       <c r="D24" s="38"/>
@@ -2533,30 +2545,30 @@
     </row>
     <row r="25">
       <c r="A25" s="45"/>
-      <c r="B25" s="50" t="s">
+      <c r="B25" s="52" t="s">
         <v>55</v>
       </c>
-      <c r="C25" s="42">
-        <v>0.5</v>
-      </c>
-      <c r="D25" s="51">
+      <c r="C25" s="53">
+        <v>1.0</v>
+      </c>
+      <c r="D25" s="55">
         <f>COUNTIF(B20:B25,"&lt;&gt;text")</f>
         <v>6</v>
       </c>
-      <c r="E25" s="51">
+      <c r="E25" s="55">
         <f>(SUM(C20:C25)/D25)*10</f>
-        <v>5</v>
+        <v>6.666666667</v>
       </c>
       <c r="F25" s="43"/>
     </row>
     <row r="26">
-      <c r="A26" s="52" t="s">
+      <c r="A26" s="56" t="s">
         <v>56</v>
       </c>
-      <c r="B26" s="53" t="s">
+      <c r="B26" s="57" t="s">
         <v>57</v>
       </c>
-      <c r="C26" s="42">
+      <c r="C26" s="58">
         <v>1.0</v>
       </c>
       <c r="D26" s="38"/>
@@ -2565,10 +2577,10 @@
     </row>
     <row r="27">
       <c r="A27" s="44"/>
-      <c r="B27" s="53" t="s">
+      <c r="B27" s="57" t="s">
         <v>58</v>
       </c>
-      <c r="C27" s="42">
+      <c r="C27" s="58">
         <v>1.0</v>
       </c>
       <c r="D27" s="38"/>
@@ -2577,30 +2589,30 @@
     </row>
     <row r="28">
       <c r="A28" s="45"/>
-      <c r="B28" s="53" t="s">
+      <c r="B28" s="57" t="s">
         <v>59</v>
       </c>
-      <c r="C28" s="42">
-        <v>0.5</v>
-      </c>
-      <c r="D28" s="51">
+      <c r="C28" s="58">
+        <v>1.0</v>
+      </c>
+      <c r="D28" s="55">
         <f>COUNTIF(B26:B28,"&lt;&gt;text")</f>
         <v>3</v>
       </c>
-      <c r="E28" s="51">
+      <c r="E28" s="55">
         <f>(SUM(C26:C28)/D28)*10</f>
-        <v>8.333333333</v>
+        <v>10</v>
       </c>
       <c r="F28" s="43"/>
     </row>
     <row r="29">
-      <c r="B29" s="54">
+      <c r="B29" s="59">
         <f>COUNTIF(B2:B28,"&lt;&gt;text")</f>
         <v>27</v>
       </c>
-      <c r="C29" s="54">
+      <c r="C29" s="59">
         <f>(SUM(C2:C28)/B29)*10</f>
-        <v>6.296296296</v>
+        <v>8.703703704</v>
       </c>
     </row>
   </sheetData>
